--- a/artfynd/A 56035-2025 artfynd.xlsx
+++ b/artfynd/A 56035-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94881095</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>305943.6733668337</v>
+        <v>305944</v>
       </c>
       <c r="R2" t="n">
-        <v>6444022.025899035</v>
+        <v>6444022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2021-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112649670</v>
+        <v>112649588</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>477</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,17 +828,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säckebäck, lokal 4, Boh</t>
+          <t>Säckebäck, lokal 1, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306249</v>
+        <v>305956</v>
       </c>
       <c r="R3" t="n">
-        <v>6444248</v>
+        <v>6444025</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +862,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>OB-Oru-0072</t>
+          <t>OB-Oru-0069</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -934,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112649691</v>
+        <v>112649615</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +944,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,14 +957,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Säckebäck, lokal 5, Boh</t>
+          <t>Säckebäck, lokal 2, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306259</v>
+        <v>306069</v>
       </c>
       <c r="R4" t="n">
-        <v>6444012</v>
+        <v>6444254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +991,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>OB-Oru-0073</t>
+          <t>OB-Oru-0070</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1046,7 +1021,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Mattsson, Olle Molander</t>
+          <t>Olle Molander, Tore Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1068,15 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112649588</v>
+        <v>112649640</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1116,17 +1086,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Säckebäck, lokal 1, Boh</t>
+          <t>Säckebäck, lokal 3, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>305956</v>
+        <v>306174</v>
       </c>
       <c r="R5" t="n">
-        <v>6444025</v>
+        <v>6444320</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1150,7 +1120,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>OB-Oru-0069</t>
+          <t>OB-Oru-0071</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1191,7 +1161,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tore Mattsson, Olle Molander</t>
+          <t>Olle Molander, Tore Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1202,15 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112649615</v>
+        <v>112649670</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1202,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,14 +1215,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Säckebäck, lokal 2, Boh</t>
+          <t>Säckebäck, lokal 4, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306069</v>
+        <v>306249</v>
       </c>
       <c r="R6" t="n">
-        <v>6444254</v>
+        <v>6444248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>OB-Oru-0070</t>
+          <t>OB-Oru-0072</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1314,7 +1279,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,6 +1294,383 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112649691</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Säckebäck, lokal 5, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>306259</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6444012</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stala</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>OB-Oru-0073</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Området planeras bebyggas</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112649708</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Säckebäck, lokal 6, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>306095</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6444401</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stala</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>OB-Oru-0074</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ung tallskog på gammal övergiven vägbana</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112649714</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Säckebäck, V om lokalväg, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>305898</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6443971</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stala</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>OB-Oru-0075</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tore Mattsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tore Mattsson, Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 56035-2025 artfynd.xlsx
+++ b/artfynd/A 56035-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94881095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649615</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649640</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,6 +1323,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1427,6 +1457,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649691</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1551,6 +1586,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649708</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1675,8 +1715,23 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649714</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>